--- a/human_validation/judge/kor/judge_D004_S005_P003__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D004_S005_P003__llama-3.3-70b-instruct_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B81"/>
+  <dimension ref="A1:B74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,439 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 걸 환영합니다. 오늘 어떤 일로 오시게 되었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 제가 사는 아파트 건물에서 몇 달째 뭔가가 벌어지고 있어서 왔어요. 관리인이랑 거기 몇몇 사람들이, 그러니까, 잘못 배달되는 우편물이나 특정 시간에 벽에서 나는 소음, 이웃들의 이런저런 말 같은 것들을 이용해서 저를 나가게 하려고 압박을 주고 있어요.
+계속 서류랑 설명을 주는데, 그런다고 제가 보고 있는 게 달라지지는 않아요. 거기엔 패턴이 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 이 일들이 실제로 일어나고 있고 서로 연결되어 있다는 증거나 근거가 있으신가요, 아니면 그냥 우연일 수도 있을까요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 그 사람들이 원하는 방식으로, 그러니까 그렇게 딱 말해주는 문서 하나로는 증명 못 해요. 근데 저는 몇 달째 이걸 지켜봐 왔어요. 우편물이 '잘못 배달'되고, 그 다음에 특정 시간에 벽에서 소음이 나고, 그러고 나면 이웃들이 거기 맞아떨어지는 작은 말들을 하죠. 그게 하나씩 따로 일어나는 일이 아니에요.
+계속 서류랑 설명을 주는데, 그런다고 제가 보는 패턴이 바뀌지는 않아요. 조직적으로 느껴져요, 저를 아파트에서 나가게 하려는 압박처럼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 본인 입장이었다면 다른 사람들도 이 패턴을 알아챘을 거라고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 네, 누구든 제 입장에서 충분히 오래 있었다면 분명 알아챘을 거예요. 한 번의 일로는 아닐지 몰라도, 몇 달을 두고 보면 분명해져요—우편물이 '잘못 배달'되고, 특정 시간에 벽에서 소음이 나고, 그 다음에 이웃들이 거기 맞아떨어지는 말을 하는 거요. 그게 제가 말하는 패턴이에요. 서류랑 설명은 제가 보고 있는 걸 딱히 바꾸지 못해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 이 일에 관련된 사람들이 특별히 본인을 표적으로 삼고 있다고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 네. 저를 특별히 겨냥하고 있다고 생각해요. 단순히 건물 전체의 일반적인 문제가 아니에요. 우편물 문제, 특정 시간에 벽에서 나는 소음, 이웃들의 작은 말들—그게 다 저랑 제 아파트를 중심으로 맞아떨어져요.
+그리고 관리인이 설명이나 서류를 줘도, 그게 딱히 그걸 바꾸지 않아요. 몇 달째 이 패턴을 봐왔고, 저를 나가게 하려고 압박하는 것처럼 느껴져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 본인을 나가게 하려는 더 큰 음모가 아파트 건물을 넘어서 존재한다고 믿으시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 건물보다 더 크다고까지 말할 수 있을지는 모르겠어요. 제가 아는 건 아파트에서 제 주변에 일어나고 있는 일이에요—관리인, 특정 이웃들, 잘못 배달되는 우편물, 특정 시간에 벽에서 나는 소음, 그리고 거기 맞아떨어지는 말들이요.
+그러니까 아니요, 무슨 큰 외부의 일이라고 말하는 건 아니에요. 근데 건물 안에서는, 네, 조직적으로 느껴지고, 저를 밀어내려는 목적처럼 느껴져요. 저한테 주는 설명이랑 서류는 그 패턴을 바꾸지 못해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 이 일들을 본인이 잘못 해석하고 있을 가능성이 있다고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 물론 생각해 봤어요. 근데 몇 달째 같은 일들이 계속 일어나고 나니까—우편물이 엉뚱한 곳으로 가고, 특정 시간에 벽에서 소음이 나고, 이웃들이 그런 작은 말들을 하는 것—저한테는 오해처럼 느껴지지 않아요.
+서류를 보여주거나 설명을 줄 수는 있는데, 그런다고 제가 보고 있는 패턴이 바뀌지는 않아요. 저를 향한 거라고 느껴져요, 저를 밀어내려는 것처럼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 시간이 지나면서 이 일들에 대한 본인의 해석이 바뀔 가능성이 있다고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 시간이 지나면 뭐든 가능하긴 하겠죠, 근데 지금은 바뀔 것 같지 않아요. 이게 몇 달째 이어지고 있어요—우편물, 특정 시간에 벽에서 나는 소음, 이웃들의 말들이요—그리고 그게 다 너무 딱 맞아떨어져요.
+관리인이 서류나 설명을 줄 수는 있는데, 그런다고 제가 보고 있는 패턴이 바뀌지는 않아요. 저한테는 여전히 저를 아파트에서 밀어내려는 압박처럼 느껴져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 사람들이 본인을 아파트에서 나가도록 압박하려 한다는 생각에 대해 본인이 틀렸을 가능성이 있다고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 추상적으로는 가능하다고 말할 수는 있겠지만, 제가 이 일에 대해 틀렸다고는 생각 안 해요. 몇 달째 관리인이랑 건물 안 몇몇 사람들이 너무 딱 맞아떨어지는 일들을 해왔기 때문에 여기 온 거예요—제 우편물이 잘못 배달되고, 특정 시간에 벽에서 소음이 나고, 이웃들이 작은 말들을 하는 거요.
+계속 설명이나 서류를 주는데, 그런다고 제가 볼 수 있는 패턴이 바뀌지 않아요. 저한테는 분명히 아파트에서 저를 내보내려는 압박이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 새로운 정보를 받으면 사람들이 본인을 아파트에서 나가도록 압박하려 한다는 믿음이 바뀔 수 있다고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 정말 새로운 정보가 있다면 봐야겠죠. 제가 듣기를 못 하는 사람이라는 건 아니에요.
+근데 솔직히, 그 사람들은 이미 서류랑 설명을 줬는데, 그게 몇 달째 제가 봐온 것—우편물이 엉뚱한 곳으로 가고, 특정 시간에 벽에서 소음이 나고, 이웃들이 그런 작은 말들을 하는 것—을 바꾸지 못해요. 저한테는 여전히 다 같은 패턴에 맞아떨어져요, 저를 아파트에서 밀어내려는 것처럼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 건물 안 모든 사람, 관리인을 포함해서, 이런 일에 전혀 관여하지 않았다고 부인한다면, 관리인과 이웃들이 본인을 나가도록 압박하려 한다는 믿음이 바뀔까요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 그 사람들이 다 부인한다고 해서 크게 바뀔 것 같지는 않아요. 솔직히 그 사람들이 부인할 거라고 예상해요.
+제게 중요한 건 몇 달째 봐온 패턴이에요—우편물이 잘못되고, 특정 시간에 벽에서 소음이 나고, 이웃들의 작은 말들이요. 관리인이 서류를 줄 수도 있고, 사람들이 관여 안 했다고 말할 수도 있지만, 그런다고 저한테는 설명이 안 돼요. 여전히 저를 아파트에서 나가게 하려는 압박처럼 보여요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 아파트 건물에서 일어나는 일에 대한 생각을 바꿀 만한 어떤 상황이 있을 수 있다고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 정말 모든 걸 명확하게 설명해 주는 상황이 있다면 고려해야겠죠. 억지를 부리려는 건 아니에요.
+근데 제 입장에서 보면, 몇 달째 우편물이 잘못 배달되고, 특정 시간에 벽에서 소음이 나고, 이웃들이 그런 작은 말들을 하는 게 다 맞아떨어져요. 그리고 관리인의 서류나 설명이 그걸 바꾸지는 못했어요. 그러니까… 이 전체 패턴을 실제로 설명하지 않는 한 뭐가 제 생각을 바꿀 수 있을지 잘 모르겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 아파트 건물에서 일어나는 일에 대한 본인의 생각을 완전히 바꿀 수 있을 만큼의 반증이 있을 수 있다고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 솔직히 말해서, 아니요, 그 사람들의 서류나 설명이 아무리 많아도 제 생각을 완전히 바꾸지는 못할 것 같아요. 그러니까 몇 달째 이걸 봐왔거든요.
+우편물이 잘못 보내지고, 특정 시간에 벽에서 소음이 나고, 특정 이웃들의 작은 말들이요—다 맞아떨어져요. 저한테는 관리인이랑 건물 안 몇몇 사람들이 저를 아파트에서 몰아내려 압박하고 있다는 게 꽤 분명해요. 그러니까 그걸 그냥 넘기는 게 아니라 그 전체 패턴을 설명해 주지 않는 한, 제가 생각을 바꿀 것 같지는 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사 질문] 본인의 믿음과 직접적으로 모순되는 증거를 제시받으면 상황에 대한 본인의 믿음을 재고할 수 있다고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 환자 응답] 그럴 것 같지는 않아요, 정말로요. 그게 그 사람들 쪽에서 나온 증거일 뿐이라면요—서류, 설명, 사람들이 안 그랬다고 말하는 것—그런 건 이미 봤고, 그게 패턴을 바꾸지는 않아요.
+몇 달째 우편물이 잘못 배달되고, 특정 시간에 벽에서 소음이 나고, 이웃들의 그런 작은 말들이 계속됐어요. 저한테는 그게 다 관리인이랑 건물 안 몇몇 사람들이 저를 밀어내려는 걸 가리켜요. 그러니까 뭔가가 그걸 반박한다 해도 전체 패턴을 설명하지 못한다면, 그냥 다시 생각해 볼 수는 없을 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사 질문] 하루에 아파트 건물 상황에 대해 얼마나 많은 시간을 생각하며 보내시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 환자 응답] 솔직히 많이요. 어떤 날은 하루의 대부분을 차지해요. 컨설팅 일 몇 개를 그만뒀는데, 이웃들이랑 관할 사무소, 건물 직원들한테 일이 어떻게 돼가는지 계속 확인하느라 그 주의 많은 시간을 쓰고 있어서요.
+그것 때문에 원래 하던 일도 방해받고, 그림 그리는 루틴도 못 지켜요. 예전처럼 자리 잡고 집중을 못 하겠어요, 계속 이걸 따라잡아야 할 것 같은 느낌이 들어서요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 제1형 양극성장애 (D008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사 질문] 아파트 건물 상황이 시작된 이후로 친구나 가족과의 관계에 변화가 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 환자 응답] 정확히 큰 변화를 느꼈는지는 잘 모르겠어요. 그러니까, 여전히 사람들이랑 얘기는 하는데, 예전만큼 시간을 내지는 못하는 것 같아요.
+어떤 친구들은 제가 왜 건물 문제에 이렇게 집중하는지 잘 이해를 못 해서, 그래서 항상 그 얘기를 꺼내지는 않아요. 가족이랑은, 좀 더… 짧게 얘기할 때가 있어요, 그 얘기 때문에 다투고 싶지 않아서요. 근데 뭔가 극적으로 관계가 끊어졌다거나 그런 건 아니에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 제1형 양극성장애 (D008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사 질문] 아파트 건물 상황에 대한 본인의 집중이 업무 능력이나 일상적인 책임을 다하는 데 영향을 미쳤나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 환자 응답] 네, 영향이 있었어요. 컨설팅 일 몇 개를 그만뒀어요, 그냥 예전처럼 그 일에 집중을 못 하게 돼서요.
+일주일 중 많은 시간을 이웃들이랑 여러 사무소, 건물 직원들한테 전화하거나 확인하면서, 무슨 일이 일어나고 있는지 계속 파악하려고 쓰고 있어요. 그러니까 평소의 루틴—일, 심부름, 심지어 그림 그리기까지—이 뒤로 밀려나요. 계속 관리하려고는 하는데, 확실히 제 책임들에 영향을 미쳤어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 제1형 양극성장애 (D008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사 질문] 아파트 건물 상황에 대한 믿음을 의심하게 만들 만한 어떤 일이나 정보가 있을 거라고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 환자 응답] 솔직히, 그럴 것 같지 않아요. 좀 답답하게 들릴 수도 있다는 건 알지만, 몇 달째 이걸 지켜봐 왔어요.
+우편물이나 소음, 사람들이 지나가면서 하는 말에 대해 서류를 보여주거나 설명을 줄 수는 있는데, 그게 전체적인 패턴을 바꾸지는 않아요. 잘못 배달된 우편물, 벽에서 나는 소음의 타이밍, 이웃들의 작은 말들—그게 저한테는 다 너무 맞아떨어져요.
+그러니까 그 모든 걸 함께 정말로 설명해 주지 않는 한, 한 번에 한 조각씩이 아니라요, 그게 제 생각을 의심하게 만들 것 같지는 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 제1형 양극성장애 (D008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사 질문] 아파트 건물에서 일어나는 일들이 그냥 우연일 가능성을 고려해 본 적이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 환자 응답] 아니요, 별로요. 그러니까, 그렇게 생각해 보려고는 했는데, 몇 달째 계속되고 있고, 한 가지 일만이 아니에요.
+우편물만이라면 그럴 수도 있죠. 아니면 벽 소음만이라면요. 근데 우편물, 소음의 타이밍, 그리고 특정 이웃들의 말이 다 함께 맞아떨어져요. 그리고 관리인의 설명이 그 패턴을 바꾸지는 않아요.
+그러니까 저한테는 우연으로 안 보여요. 저를 아파트에서 나가게 하려는 압박처럼 느껴져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 제1형 양극성장애 (D008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사 질문] 이 모든 일들에 대해 아주 설득력 있는 설명을 제시받으면 아파트 건물에서 일어나는 일에 대한 생각을 바꿀 수 있을까요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 환자 응답] 정말 그 모든 걸 함께 다 아우르는 설명이 있다면 들어봐야겠죠. 근데 솔직히 그게 어떻게 가능할지 모르겠어요.
+관리인이 서류를 보여줄 수도 있고, 사람들이 우편물 착오는 사고라고, 벽 소음은 정상이라고 말할 수도 있어요. 근데 그게 몇 달째 제가 봐온 전체 패턴—우편물, 소음의 타이밍, 특정 이웃들의 말들—을 설명해 주지는 않아요.
+그러니까, 아니요, 그 사람들이 또 다른 설명을 준다고 해서 제가 생각을 바꿀 것 같지는 않아요. 모든 걸 다 설명해야 할 텐데, 지금까지는 아무것도 그러지 못했어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 제1형 양극성장애 (D008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
         <is>
           <t>진단명: 망상장애 (D004)
 인구통계: 성별 남성 / 나이 65 / 직업상태 management analyst / 최종학력 대학원 졸업
@@ -575,488 +999,29 @@
 증상 지속 기간: 11 months
 추가 요건: Functioning is not markedly impaired apart from the impact of the delusion(s) or its ramifications
 주호소 증상 코드: S019
-배경 서술: 마르완은 오랫동안 살던 엔디컷의 집을 정리하고 갤러리와 핑거레이크스 근처의 더 작은 아파트로 이사했는데, 이는 컨설팅 업무를 단순화하고 그림을 그릴 시간을 더 확보하려는 의도에서였다. 이사 후 뒤따른 잘못 배달된 우편물, 낯선 건물 소음, 관리인과의 마찰 같은 작은 문제들이 시작점이 되어, 이후 11개월 동안 실질적인 설명과 문서 증거에도 불구하고 흔들리지 않는 고정된 믿음으로 굳어졌다. 그 믿음이 점점 더 그의 삶의 중심이 되면서, 그는 여러 컨설팅 업무에서 손을 떼고, 이웃과 관할 사무소에 반복적으로 확인을 요청했으며, 예전에 하루하루를 지탱해 주던 일상 속으로 점점 더 자리 잡지 못하게 되었다. 그는 주거 문제에 관한 지역사회 중재 모임이 중재자와 1차 진료 의사가 함께 긴급 정신건강 평가를 권고하는 것으로 끝난 뒤 정신과 진료를 받게 되었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 걸 환영합니다. 오늘 어떤 일로 오시게 되었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 제가 사는 아파트 건물에서 몇 달째 뭔가가 벌어지고 있어서 왔어요. 관리인이랑 거기 몇몇 사람들이, 그러니까, 잘못 배달되는 우편물이나 특정 시간에 벽에서 나는 소음, 이웃들의 이런저런 말 같은 것들을 이용해서 저를 나가게 하려고 압박을 주고 있어요.
-계속 서류랑 설명을 주는데, 그런다고 제가 보고 있는 게 달라지지는 않아요. 거기엔 패턴이 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 이 일들이 실제로 일어나고 있고 서로 연결되어 있다는 증거나 근거가 있으신가요, 아니면 그냥 우연일 수도 있을까요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 그 사람들이 원하는 방식으로, 그러니까 그렇게 딱 말해주는 문서 하나로는 증명 못 해요. 근데 저는 몇 달째 이걸 지켜봐 왔어요. 우편물이 '잘못 배달'되고, 그 다음에 특정 시간에 벽에서 소음이 나고, 그러고 나면 이웃들이 거기 맞아떨어지는 작은 말들을 하죠. 그게 하나씩 따로 일어나는 일이 아니에요.
-계속 서류랑 설명을 주는데, 그런다고 제가 보는 패턴이 바뀌지는 않아요. 조직적으로 느껴져요, 저를 아파트에서 나가게 하려는 압박처럼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 본인 입장이었다면 다른 사람들도 이 패턴을 알아챘을 거라고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 네, 누구든 제 입장에서 충분히 오래 있었다면 분명 알아챘을 거예요. 한 번의 일로는 아닐지 몰라도, 몇 달을 두고 보면 분명해져요—우편물이 '잘못 배달'되고, 특정 시간에 벽에서 소음이 나고, 그 다음에 이웃들이 거기 맞아떨어지는 말을 하는 거요. 그게 제가 말하는 패턴이에요. 서류랑 설명은 제가 보고 있는 걸 딱히 바꾸지 못해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 이 일에 관련된 사람들이 특별히 본인을 표적으로 삼고 있다고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 네. 저를 특별히 겨냥하고 있다고 생각해요. 단순히 건물 전체의 일반적인 문제가 아니에요. 우편물 문제, 특정 시간에 벽에서 나는 소음, 이웃들의 작은 말들—그게 다 저랑 제 아파트를 중심으로 맞아떨어져요.
-그리고 관리인이 설명이나 서류를 줘도, 그게 딱히 그걸 바꾸지 않아요. 몇 달째 이 패턴을 봐왔고, 저를 나가게 하려고 압박하는 것처럼 느껴져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 본인을 나가게 하려는 더 큰 음모가 아파트 건물을 넘어서 존재한다고 믿으시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 건물보다 더 크다고까지 말할 수 있을지는 모르겠어요. 제가 아는 건 아파트에서 제 주변에 일어나고 있는 일이에요—관리인, 특정 이웃들, 잘못 배달되는 우편물, 특정 시간에 벽에서 나는 소음, 그리고 거기 맞아떨어지는 말들이요.
-그러니까 아니요, 무슨 큰 외부의 일이라고 말하는 건 아니에요. 근데 건물 안에서는, 네, 조직적으로 느껴지고, 저를 밀어내려는 목적처럼 느껴져요. 저한테 주는 설명이랑 서류는 그 패턴을 바꾸지 못해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 이 일들을 본인이 잘못 해석하고 있을 가능성이 있다고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 물론 생각해 봤어요. 근데 몇 달째 같은 일들이 계속 일어나고 나니까—우편물이 엉뚱한 곳으로 가고, 특정 시간에 벽에서 소음이 나고, 이웃들이 그런 작은 말들을 하는 것—저한테는 오해처럼 느껴지지 않아요.
-서류를 보여주거나 설명을 줄 수는 있는데, 그런다고 제가 보고 있는 패턴이 바뀌지는 않아요. 저를 향한 거라고 느껴져요, 저를 밀어내려는 것처럼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 시간이 지나면서 이 일들에 대한 본인의 해석이 바뀔 가능성이 있다고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 시간이 지나면 뭐든 가능하긴 하겠죠, 근데 지금은 바뀔 것 같지 않아요. 이게 몇 달째 이어지고 있어요—우편물, 특정 시간에 벽에서 나는 소음, 이웃들의 말들이요—그리고 그게 다 너무 딱 맞아떨어져요.
-관리인이 서류나 설명을 줄 수는 있는데, 그런다고 제가 보고 있는 패턴이 바뀌지는 않아요. 저한테는 여전히 저를 아파트에서 밀어내려는 압박처럼 느껴져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 사람들이 본인을 아파트에서 나가도록 압박하려 한다는 생각에 대해 본인이 틀렸을 가능성이 있다고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 추상적으로는 가능하다고 말할 수는 있겠지만, 제가 이 일에 대해 틀렸다고는 생각 안 해요. 몇 달째 관리인이랑 건물 안 몇몇 사람들이 너무 딱 맞아떨어지는 일들을 해왔기 때문에 여기 온 거예요—제 우편물이 잘못 배달되고, 특정 시간에 벽에서 소음이 나고, 이웃들이 작은 말들을 하는 거요.
-계속 설명이나 서류를 주는데, 그런다고 제가 볼 수 있는 패턴이 바뀌지 않아요. 저한테는 분명히 아파트에서 저를 내보내려는 압박이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 새로운 정보를 받으면 사람들이 본인을 아파트에서 나가도록 압박하려 한다는 믿음이 바뀔 수 있다고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 정말 새로운 정보가 있다면 봐야겠죠. 제가 듣기를 못 하는 사람이라는 건 아니에요.
-근데 솔직히, 그 사람들은 이미 서류랑 설명을 줬는데, 그게 몇 달째 제가 봐온 것—우편물이 엉뚱한 곳으로 가고, 특정 시간에 벽에서 소음이 나고, 이웃들이 그런 작은 말들을 하는 것—을 바꾸지 못해요. 저한테는 여전히 다 같은 패턴에 맞아떨어져요, 저를 아파트에서 밀어내려는 것처럼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 건물 안 모든 사람, 관리인을 포함해서, 이런 일에 전혀 관여하지 않았다고 부인한다면, 관리인과 이웃들이 본인을 나가도록 압박하려 한다는 믿음이 바뀔까요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 그 사람들이 다 부인한다고 해서 크게 바뀔 것 같지는 않아요. 솔직히 그 사람들이 부인할 거라고 예상해요.
-제게 중요한 건 몇 달째 봐온 패턴이에요—우편물이 잘못되고, 특정 시간에 벽에서 소음이 나고, 이웃들의 작은 말들이요. 관리인이 서류를 줄 수도 있고, 사람들이 관여 안 했다고 말할 수도 있지만, 그런다고 저한테는 설명이 안 돼요. 여전히 저를 아파트에서 나가게 하려는 압박처럼 보여요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 아파트 건물에서 일어나는 일에 대한 생각을 바꿀 만한 어떤 상황이 있을 수 있다고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 정말 모든 걸 명확하게 설명해 주는 상황이 있다면 고려해야겠죠. 억지를 부리려는 건 아니에요.
-근데 제 입장에서 보면, 몇 달째 우편물이 잘못 배달되고, 특정 시간에 벽에서 소음이 나고, 이웃들이 그런 작은 말들을 하는 게 다 맞아떨어져요. 그리고 관리인의 서류나 설명이 그걸 바꾸지는 못했어요. 그러니까… 이 전체 패턴을 실제로 설명하지 않는 한 뭐가 제 생각을 바꿀 수 있을지 잘 모르겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 아파트 건물에서 일어나는 일에 대한 본인의 생각을 완전히 바꿀 수 있을 만큼의 반증이 있을 수 있다고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 솔직히 말해서, 아니요, 그 사람들의 서류나 설명이 아무리 많아도 제 생각을 완전히 바꾸지는 못할 것 같아요. 그러니까 몇 달째 이걸 봐왔거든요.
-우편물이 잘못 보내지고, 특정 시간에 벽에서 소음이 나고, 특정 이웃들의 작은 말들이요—다 맞아떨어져요. 저한테는 관리인이랑 건물 안 몇몇 사람들이 저를 아파트에서 몰아내려 압박하고 있다는 게 꽤 분명해요. 그러니까 그걸 그냥 넘기는 게 아니라 그 전체 패턴을 설명해 주지 않는 한, 제가 생각을 바꿀 것 같지는 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사 질문] 본인의 믿음과 직접적으로 모순되는 증거를 제시받으면 상황에 대한 본인의 믿음을 재고할 수 있다고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 환자 응답] 그럴 것 같지는 않아요, 정말로요. 그게 그 사람들 쪽에서 나온 증거일 뿐이라면요—서류, 설명, 사람들이 안 그랬다고 말하는 것—그런 건 이미 봤고, 그게 패턴을 바꾸지는 않아요.
-몇 달째 우편물이 잘못 배달되고, 특정 시간에 벽에서 소음이 나고, 이웃들의 그런 작은 말들이 계속됐어요. 저한테는 그게 다 관리인이랑 건물 안 몇몇 사람들이 저를 밀어내려는 걸 가리켜요. 그러니까 뭔가가 그걸 반박한다 해도 전체 패턴을 설명하지 못한다면, 그냥 다시 생각해 볼 수는 없을 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사 질문] 하루에 아파트 건물 상황에 대해 얼마나 많은 시간을 생각하며 보내시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 환자 응답] 솔직히 많이요. 어떤 날은 하루의 대부분을 차지해요. 컨설팅 일 몇 개를 그만뒀는데, 이웃들이랑 관할 사무소, 건물 직원들한테 일이 어떻게 돼가는지 계속 확인하느라 그 주의 많은 시간을 쓰고 있어서요.
-그것 때문에 원래 하던 일도 방해받고, 그림 그리는 루틴도 못 지켜요. 예전처럼 자리 잡고 집중을 못 하겠어요, 계속 이걸 따라잡아야 할 것 같은 느낌이 들어서요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 제1형 양극성장애 (D008)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사 질문] 아파트 건물 상황이 시작된 이후로 친구나 가족과의 관계에 변화가 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 환자 응답] 정확히 큰 변화를 느꼈는지는 잘 모르겠어요. 그러니까, 여전히 사람들이랑 얘기는 하는데, 예전만큼 시간을 내지는 못하는 것 같아요.
-어떤 친구들은 제가 왜 건물 문제에 이렇게 집중하는지 잘 이해를 못 해서, 그래서 항상 그 얘기를 꺼내지는 않아요. 가족이랑은, 좀 더… 짧게 얘기할 때가 있어요, 그 얘기 때문에 다투고 싶지 않아서요. 근데 뭔가 극적으로 관계가 끊어졌다거나 그런 건 아니에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 제1형 양극성장애 (D008)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사 질문] 아파트 건물 상황에 대한 본인의 집중이 업무 능력이나 일상적인 책임을 다하는 데 영향을 미쳤나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 환자 응답] 네, 영향이 있었어요. 컨설팅 일 몇 개를 그만뒀어요, 그냥 예전처럼 그 일에 집중을 못 하게 돼서요.
-일주일 중 많은 시간을 이웃들이랑 여러 사무소, 건물 직원들한테 전화하거나 확인하면서, 무슨 일이 일어나고 있는지 계속 파악하려고 쓰고 있어요. 그러니까 평소의 루틴—일, 심부름, 심지어 그림 그리기까지—이 뒤로 밀려나요. 계속 관리하려고는 하는데, 확실히 제 책임들에 영향을 미쳤어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 제1형 양극성장애 (D008)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사 질문] 아파트 건물 상황에 대한 믿음을 의심하게 만들 만한 어떤 일이나 정보가 있을 거라고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 환자 응답] 솔직히, 그럴 것 같지 않아요. 좀 답답하게 들릴 수도 있다는 건 알지만, 몇 달째 이걸 지켜봐 왔어요.
-우편물이나 소음, 사람들이 지나가면서 하는 말에 대해 서류를 보여주거나 설명을 줄 수는 있는데, 그게 전체적인 패턴을 바꾸지는 않아요. 잘못 배달된 우편물, 벽에서 나는 소음의 타이밍, 이웃들의 작은 말들—그게 저한테는 다 너무 맞아떨어져요.
-그러니까 그 모든 걸 함께 정말로 설명해 주지 않는 한, 한 번에 한 조각씩이 아니라요, 그게 제 생각을 의심하게 만들 것 같지는 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 제1형 양극성장애 (D008)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사 질문] 아파트 건물에서 일어나는 일들이 그냥 우연일 가능성을 고려해 본 적이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 환자 응답] 아니요, 별로요. 그러니까, 그렇게 생각해 보려고는 했는데, 몇 달째 계속되고 있고, 한 가지 일만이 아니에요.
-우편물만이라면 그럴 수도 있죠. 아니면 벽 소음만이라면요. 근데 우편물, 소음의 타이밍, 그리고 특정 이웃들의 말이 다 함께 맞아떨어져요. 그리고 관리인의 설명이 그 패턴을 바꾸지는 않아요.
-그러니까 저한테는 우연으로 안 보여요. 저를 아파트에서 나가게 하려는 압박처럼 느껴져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 제1형 양극성장애 (D008)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사 질문] 이 모든 일들에 대해 아주 설득력 있는 설명을 제시받으면 아파트 건물에서 일어나는 일에 대한 생각을 바꿀 수 있을까요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 환자 응답] 정말 그 모든 걸 함께 다 아우르는 설명이 있다면 들어봐야겠죠. 근데 솔직히 그게 어떻게 가능할지 모르겠어요.
-관리인이 서류를 보여줄 수도 있고, 사람들이 우편물 착오는 사고라고, 벽 소음은 정상이라고 말할 수도 있어요. 근데 그게 몇 달째 제가 봐온 전체 패턴—우편물, 소음의 타이밍, 특정 이웃들의 말들—을 설명해 주지는 않아요.
-그러니까, 아니요, 그 사람들이 또 다른 설명을 준다고 해서 제가 생각을 바꿀 것 같지는 않아요. 모든 걸 다 설명해야 할 텐데, 지금까지는 아무것도 그러지 못했어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
+배경 서술: 마르완은 오랫동안 살던 엔디컷의 집을 정리하고 갤러리와 핑거레이크스 근처의 더 작은 아파트로 이사했는데, 이는 컨설팅 업무를 단순화하고 그림을 그릴 시간을 더 확보하려는 의도에서였다. 이사 후 뒤따른 잘못 배달된 우편물, 낯선 건물 소음, 관리인과의 마찰 같은 작은 문제들이 시작점이 되어, 이후 11개월 동안 실질적인 설명과 문서 증거에도 불구하고 흔들리지 않는 고정된 믿음으로 굳어졌다. 그 믿음이 점점 더 그의 삶의 중심이 되면서, 그는 여러 컨설팅 업무에서 손을 떼고, 이웃과 관할 사무소에 반복적으로 확인을 요청했으며, 예전에 하루하루를 지탱해 주던 일상 속으로 점점 더 자리 잡지 못하게 되었다. 그는 주거 문제에 관한 지역사회 중재 모임이 중재자와 1차 진료 의사가 함께 긴급 정신건강 평가를 권고하는 것으로 끝난 뒤 정신과 진료를 받게 되었다.
+표집된 증상 목록:
+  - S019 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.</t>
+        </is>
+      </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>[19번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 제1형 양극성장애 (D008)</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 망상장애 (D004, ICD: F22)</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: delusions (관계=must_include, 요구개수=1, 충족개수=1, 커버리지=1.0)
-  확인된 근거: 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.
-  누락: (없음)</t>
+          <t>의사의 최종 진단: 망상장애 (D004, ICD: F22)
+지속 기간 요건: 있음
+기능적 손상 요건: None
+추가 요건: 없음
+체크리스트 그룹: delusions (관계=must_include, 요구개수=1, 충족개수=1, 커버리지=1.0)
+확인된 근거:
+  - 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A73:B73"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D004_S005_P003__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D004_S005_P003__llama-3.3-70b-instruct_kor.xlsx
@@ -985,6 +985,11 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -1017,11 +1022,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A73:B73"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D004_S005_P003__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D004_S005_P003__llama-3.3-70b-instruct_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.1404</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.1404</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -555,6 +556,7 @@
         <v>0.6667</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
